--- a/audit-autogen-project/data/mapping_file.xlsx
+++ b/audit-autogen-project/data/mapping_file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\审计自动化\audit_autogen_project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60F134ED-5EA1-4AEB-9792-D3C2EA713C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A31C7FE-2DB6-4EC9-B175-9691DBBB144B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="资产负债表区块" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="322">
   <si>
     <t>科目名称</t>
   </si>
@@ -686,515 +686,535 @@
     <t>B58</t>
   </si>
   <si>
+    <t>B61</t>
+  </si>
+  <si>
+    <t>B64</t>
+  </si>
+  <si>
+    <t>流动资产合计</t>
+  </si>
+  <si>
+    <t>B14</t>
+  </si>
+  <si>
+    <t>C14</t>
+  </si>
+  <si>
+    <t>资产总计</t>
+  </si>
+  <si>
+    <t>C64</t>
+  </si>
+  <si>
+    <t>净资产合计</t>
+  </si>
+  <si>
+    <t>B63</t>
+  </si>
+  <si>
+    <t>C63</t>
+  </si>
+  <si>
+    <t>规则</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>字段名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>期初</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>期初日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>期末</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>期末日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单位名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B4,B36</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C4,C36</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>说明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>标准科目名为模板中的名称，等价名为源数据或其他名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只要是和模板不一样的都填上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存货</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一年内到期的非流动资产</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存  货</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一年内到期的长期债权投资</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一年内到期的非流动负债</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">预付款项 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>固定资产</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>应付款项</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>应收款项</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>应付账款</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>应收账款</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否计算</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>G</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>长期投资：,固定资产：,固定资产合计,无形资产：,受托代理资产：,</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>收入汇总</t>
+  </si>
+  <si>
+    <t>支出汇总</t>
+  </si>
+  <si>
+    <t>收支结余汇总</t>
+  </si>
+  <si>
+    <t>模板</t>
+  </si>
+  <si>
+    <t>期初单元格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>期末单元格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文字模板</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拆分并判断最后1天</t>
+  </si>
+  <si>
+    <t>HeaderMapping</t>
+  </si>
+  <si>
+    <t>备注（可选）</t>
+  </si>
+  <si>
+    <t>注入单元格</t>
+  </si>
+  <si>
+    <t>计算方式</t>
+  </si>
+  <si>
+    <t>来源Sheet</t>
+  </si>
+  <si>
+    <t>{{收入汇总}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{支出汇总}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{收支结余汇总}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{起始日期}}、{{终止日期}}、{{审计期间}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>strip("编制单位:")</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>=期末-期初</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>K1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不用填写，已在mapping_file中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不用填写，已在mapping_file中，如果有问题，检查是否填写到月份</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不管</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>注意核对无误</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{单位名称}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>期末</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2021业务活动表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>源期初坐标</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>源期初坐标可不写，因为默认业务活动表期初的期初为0，如果对方提供了期初的期初手动添加即可</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检查源数据有没有“商品销售收入”，有的话跳过即可，或者在t.xlsx和本表格中新增一行并填写坐标</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>源数据有就填，没有可以不填，会自动计算</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>起始资产负债表Sheet</t>
+  </si>
+  <si>
+    <t>终止资产负债表Sheet</t>
+  </si>
+  <si>
+    <t>Sheet名</t>
+  </si>
+  <si>
+    <t>起始业务活动表Sheet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>终止业务活动表Sheet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资产负债表区块</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>=收入-支出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>期初资产总额</t>
+  </si>
+  <si>
+    <t>期末资产总额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>期初负债总额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>期末负债总额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>期初净资产总额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>期末净资产总额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{期初资产总额}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{期末资产总额}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{期初负债总额}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{期末负债总额}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{期初净资产总额}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{期末净资产总额}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资产负债表区块</t>
+  </si>
+  <si>
+    <t>资产总额增减</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{资产总额增减}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>负债总额增减</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>净资产总额增减</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{负债总额增减}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{净资产总额增减}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>编制单位：联合会新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2021年1月-2025年5月</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2021资产负债表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025资产负债表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025业务活动表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资产总额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>负债总额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>负债合计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>净资产总额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E33</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B58</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C58</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C13</t>
+  </si>
+  <si>
+    <t>C10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等价科目名1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等价科目名2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>固定资产原价</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一年内到期的长期负债</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有者权益</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>长期负债：,受托代理负债：,净资产：,</t>
-  </si>
-  <si>
-    <t>B61</t>
-  </si>
-  <si>
-    <t>B64</t>
-  </si>
-  <si>
-    <t>流动资产合计</t>
-  </si>
-  <si>
-    <t>B14</t>
-  </si>
-  <si>
-    <t>C14</t>
-  </si>
-  <si>
-    <t>非流动资产合计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>C30</t>
-  </si>
-  <si>
-    <t>资产总计</t>
-  </si>
-  <si>
-    <t>B35</t>
-  </si>
-  <si>
-    <t>C35</t>
-  </si>
-  <si>
-    <t>C64</t>
-  </si>
-  <si>
-    <t>净资产合计</t>
-  </si>
-  <si>
-    <t>B63</t>
-  </si>
-  <si>
-    <t>C63</t>
-  </si>
-  <si>
-    <t>规则</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>字段名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>期初</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>期初日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>期末</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>期末日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单位名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>B4,B36</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>C4,C36</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>说明</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>标准科目名为模板中的名称，等价名为源数据或其他名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>只要是和模板不一样的都填上</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>存货</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一年内到期的非流动资产</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>存  货</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一年内到期的长期债权投资</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一年内到期的非流动负债</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">预付款项 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>固定资产</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>应付款项</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>应收款项</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>应付账款</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>应收账款</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否计算</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>否</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A13</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>D34</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>D</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>G</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>H</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>长期投资：,固定资产：,固定资产合计,无形资产：,受托代理资产：,</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>收入汇总</t>
-  </si>
-  <si>
-    <t>支出汇总</t>
-  </si>
-  <si>
-    <t>收支结余汇总</t>
-  </si>
-  <si>
-    <t>模板</t>
-  </si>
-  <si>
-    <t>期初单元格</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>期末单元格</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>文字模板</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>拆分并判断最后1天</t>
-  </si>
-  <si>
-    <t>HeaderMapping</t>
-  </si>
-  <si>
-    <t>备注（可选）</t>
-  </si>
-  <si>
-    <t>注入单元格</t>
-  </si>
-  <si>
-    <t>计算方式</t>
-  </si>
-  <si>
-    <t>来源Sheet</t>
-  </si>
-  <si>
-    <t>{{收入汇总}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{支出汇总}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{收支结余汇总}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{起始日期}}、{{终止日期}}、{{审计期间}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>strip("编制单位:")</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>=期末-期初</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>K1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不用填写，已在mapping_file中</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不用填写，已在mapping_file中，如果有问题，检查是否填写到月份</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不管</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>注意核对无误</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{单位名称}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>期末</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2021业务活动表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>源期初坐标</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>源期初坐标可不写，因为默认业务活动表期初的期初为0，如果对方提供了期初的期初手动添加即可</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>检查源数据有没有“商品销售收入”，有的话跳过即可，或者在t.xlsx和本表格中新增一行并填写坐标</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>源数据有就填，没有可以不填，会自动计算</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>起始资产负债表Sheet</t>
-  </si>
-  <si>
-    <t>终止资产负债表Sheet</t>
-  </si>
-  <si>
-    <t>Sheet名</t>
-  </si>
-  <si>
-    <t>起始业务活动表Sheet</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>终止业务活动表Sheet</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>资产负债表区块</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>=收入-支出</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>期初资产总额</t>
-  </si>
-  <si>
-    <t>期末资产总额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>期初负债总额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>期末负债总额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>期初净资产总额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>期末净资产总额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{期初资产总额}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{期末资产总额}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{期初负债总额}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{期末负债总额}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{期初净资产总额}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{期末净资产总额}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>资产负债表区块</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资产变化方向</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{资产变化方向}}</t>
+  </si>
+  <si>
+    <t>负债变化方向</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{负债变化方向}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>净资产变化方向</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{净资产变化方向}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{{起始日期}}，{{单位名称}}资产总额为{{期初资产总额}}元，负债总额为{{期初负债总额}}元，净资产总额为{{期初净资产总额}}元。
 {{终止日期}}，{{单位名称}}资产总额为{{期末资产总额}}元，负债总额为{{期末负债总额}}元，净资产总额为{{期末净资产总额}}元。
-与本届开始日相比，{{单位名称}}的资产总额{{资产变化方向}}{{资产变动额}}元，负债总额{{负债变化方向}}{{负债变动额}}元，净资产总额{{净资产变化方向}}{{净资产变动额}}元。业务活动正常。                                                           {{审计期间}}，{{单位名称}}实现各项收入总额{{收入汇总}}元，发生各项费用支出总额为{{支出汇总}}元，收支结余总额为{{收支结余汇总}}元。
+与本届开始日相比，{{单位名称}}的资产总额{{资产变化方向}}{{资产总额增减}}元，负债总额{{负债变化方向}}{{负债总额增减}}元，净资产总额{{净资产变化方向}}{{净资产总额增减}}元。业务活动正常。                                                           {{审计期间}}，{{单位名称}}实现各项收入总额{{收入汇总}}元，发生各项费用支出总额为{{支出汇总}}元，收支结余总额为{{收支结余汇总}}元。
 {{审计期间}}，{{单位名称}}收入情况如表4所示，成本费用情况如表5所示。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>资产总额增减</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{资产总额增减}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>负债总额增减</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>净资产总额增减</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{负债总额增减}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{净资产总额增减}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>编制单位：联合会新</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2021年1月-2025年5月</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2021资产负债表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025资产负债表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025业务活动表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>资产总额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>负债总额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>负债合计</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>净资产总额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>E5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>E17</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>E31</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>E33</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>E25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>E14</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>E24</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>B58</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>C58</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>C13</t>
-  </si>
-  <si>
-    <t>C10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>C15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>等价科目名1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>等价科目名2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>固定资产原价</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一年内到期的长期负债</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>所有者权益</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1347,7 +1367,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1494,11 +1514,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1805,7 +1828,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="4" width="20.75" customWidth="1"/>
@@ -1853,16 +1876,16 @@
         <v>40</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>169</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>171</v>
@@ -1889,10 +1912,10 @@
         <v>175</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>171</v>
@@ -1907,7 +1930,7 @@
         <v>177</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.15">
@@ -1915,16 +1938,16 @@
         <v>42</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>171</v>
@@ -1945,16 +1968,16 @@
         <v>180</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>171</v>
@@ -1969,7 +1992,7 @@
         <v>182</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>183</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.15">
@@ -1977,16 +2000,16 @@
         <v>43</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>171</v>
@@ -1995,28 +2018,28 @@
         <v>170</v>
       </c>
       <c r="H6" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="I6" s="12" t="s">
         <v>184</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>185</v>
       </c>
       <c r="J6" s="12"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A7" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>171</v>
@@ -2025,24 +2048,28 @@
         <v>170</v>
       </c>
       <c r="H7" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="I7" s="12" t="s">
         <v>187</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>188</v>
       </c>
       <c r="J7" s="12"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A8" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
+        <v>188</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>175</v>
+      </c>
       <c r="D8" s="12" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>171</v>
@@ -2051,28 +2078,28 @@
         <v>170</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>177</v>
+        <v>312</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>190</v>
+        <v>313</v>
       </c>
       <c r="J8" s="12"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A9" s="12" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>175</v>
+        <v>314</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>175</v>
+        <v>314</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>171</v>
@@ -2081,28 +2108,28 @@
         <v>170</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="J9" s="12"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A10" s="12" t="s">
-        <v>159</v>
+        <v>190</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F10" s="12" t="s">
         <v>171</v>
@@ -2111,28 +2138,28 @@
         <v>170</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J10" s="12"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A11" s="12" t="s">
-        <v>195</v>
+      <c r="A11" s="51" t="s">
+        <v>292</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>227</v>
+        <v>298</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>227</v>
+        <v>298</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>231</v>
+        <v>224</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>171</v>
@@ -2141,41 +2168,16 @@
         <v>170</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>196</v>
+        <v>301</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="J11" s="12"/>
+        <v>302</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A12" s="51" t="s">
-        <v>299</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>305</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>305</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>308</v>
-      </c>
-      <c r="I12" s="12" t="s">
-        <v>309</v>
-      </c>
+      <c r="A12" s="2"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A13" s="2"/>
@@ -2188,7 +2190,7 @@
       <c r="C14" s="12"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A15" s="2"/>
+      <c r="A15" s="4"/>
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
     </row>
@@ -2198,17 +2200,17 @@
       <c r="C16" s="12"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A17" s="4"/>
+      <c r="A17" s="2"/>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A18" s="2"/>
+      <c r="A18" s="4"/>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A19" s="4"/>
+      <c r="A19" s="2"/>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
     </row>
@@ -2223,12 +2225,12 @@
       <c r="C21" s="12"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A22" s="2"/>
+      <c r="A22" s="5"/>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A23" s="5"/>
+      <c r="A23" s="6"/>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
     </row>
@@ -2238,12 +2240,12 @@
       <c r="C24" s="12"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A25" s="6"/>
+      <c r="A25" s="7"/>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A26" s="7"/>
+      <c r="A26" s="6"/>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
     </row>
@@ -2323,24 +2325,19 @@
       <c r="C41" s="12"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A42" s="6"/>
+      <c r="A42" s="2"/>
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A43" s="2"/>
+      <c r="A43" s="6"/>
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A44" s="6"/>
+      <c r="A44" s="3"/>
       <c r="B44" s="12"/>
       <c r="C44" s="12"/>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A45" s="3"/>
-      <c r="B45" s="12"/>
-      <c r="C45" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2350,7 +2347,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60E1BAD6-1745-4E67-9007-A7E50B662530}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="28.75" style="43" customWidth="1"/>
@@ -2369,81 +2366,81 @@
         <v>66</v>
       </c>
       <c r="B1" s="44" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="C1" s="44" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="D1" s="44" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E1" s="44" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F1" s="24" t="s">
         <v>128</v>
       </c>
       <c r="G1" s="24" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="H1" s="24" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="I1" s="24" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A2" s="27" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="C2" s="45" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="D2" s="45"/>
       <c r="E2" s="46"/>
       <c r="F2" s="46"/>
       <c r="G2" s="47" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="H2" s="47"/>
       <c r="I2" s="48" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A3" s="27" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="C3" s="45" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D3" s="45"/>
       <c r="E3" s="46"/>
       <c r="F3" s="46"/>
       <c r="G3" s="47" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="H3" s="47"/>
       <c r="I3" s="48" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A4" s="46" t="s">
+        <v>266</v>
+      </c>
+      <c r="B4" s="46" t="s">
+        <v>264</v>
+      </c>
+      <c r="C4" s="45" t="s">
         <v>272</v>
-      </c>
-      <c r="B4" s="46" t="s">
-        <v>270</v>
-      </c>
-      <c r="C4" s="45" t="s">
-        <v>278</v>
       </c>
       <c r="D4" s="45"/>
       <c r="E4" s="46"/>
@@ -2454,13 +2451,13 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A5" s="46" t="s">
+        <v>267</v>
+      </c>
+      <c r="B5" s="46" t="s">
+        <v>264</v>
+      </c>
+      <c r="C5" s="45" t="s">
         <v>273</v>
-      </c>
-      <c r="B5" s="46" t="s">
-        <v>270</v>
-      </c>
-      <c r="C5" s="45" t="s">
-        <v>279</v>
       </c>
       <c r="D5" s="45"/>
       <c r="E5" s="46"/>
@@ -2471,13 +2468,13 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A6" s="46" t="s">
+        <v>268</v>
+      </c>
+      <c r="B6" s="46" t="s">
+        <v>264</v>
+      </c>
+      <c r="C6" s="45" t="s">
         <v>274</v>
-      </c>
-      <c r="B6" s="46" t="s">
-        <v>270</v>
-      </c>
-      <c r="C6" s="45" t="s">
-        <v>280</v>
       </c>
       <c r="D6" s="45"/>
       <c r="E6" s="46"/>
@@ -2488,13 +2485,13 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A7" s="46" t="s">
+        <v>269</v>
+      </c>
+      <c r="B7" s="46" t="s">
+        <v>264</v>
+      </c>
+      <c r="C7" s="45" t="s">
         <v>275</v>
-      </c>
-      <c r="B7" s="46" t="s">
-        <v>270</v>
-      </c>
-      <c r="C7" s="45" t="s">
-        <v>281</v>
       </c>
       <c r="D7" s="45"/>
       <c r="E7" s="46"/>
@@ -2505,13 +2502,13 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A8" s="46" t="s">
+        <v>270</v>
+      </c>
+      <c r="B8" s="46" t="s">
+        <v>264</v>
+      </c>
+      <c r="C8" s="45" t="s">
         <v>276</v>
-      </c>
-      <c r="B8" s="46" t="s">
-        <v>270</v>
-      </c>
-      <c r="C8" s="45" t="s">
-        <v>282</v>
       </c>
       <c r="D8" s="45"/>
       <c r="E8" s="46"/>
@@ -2522,13 +2519,13 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A9" s="46" t="s">
+        <v>271</v>
+      </c>
+      <c r="B9" s="46" t="s">
+        <v>264</v>
+      </c>
+      <c r="C9" s="45" t="s">
         <v>277</v>
-      </c>
-      <c r="B9" s="46" t="s">
-        <v>270</v>
-      </c>
-      <c r="C9" s="45" t="s">
-        <v>283</v>
       </c>
       <c r="D9" s="45"/>
       <c r="E9" s="46"/>
@@ -2539,165 +2536,210 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A10" s="46" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="B10" s="46" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C10" s="45" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="D10" s="45"/>
       <c r="E10" s="46"/>
       <c r="F10" s="46"/>
       <c r="G10" s="49" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="H10" s="47"/>
       <c r="I10" s="48"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A11" s="46" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="B11" s="46" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C11" s="45" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D11" s="45"/>
       <c r="E11" s="46"/>
       <c r="F11" s="46"/>
       <c r="G11" s="49" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="H11" s="47"/>
       <c r="I11" s="48"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A12" s="46" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B12" s="46" t="s">
+        <v>278</v>
+      </c>
+      <c r="C12" s="45" t="s">
         <v>284</v>
-      </c>
-      <c r="C12" s="45" t="s">
-        <v>291</v>
       </c>
       <c r="D12" s="45"/>
       <c r="E12" s="46"/>
       <c r="F12" s="46"/>
       <c r="G12" s="49" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="H12" s="47"/>
       <c r="I12" s="48"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A13" s="46" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B13" s="46"/>
       <c r="C13" s="45" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="D13" s="45"/>
       <c r="E13" s="46"/>
       <c r="F13" s="46"/>
       <c r="G13" s="49"/>
       <c r="H13" s="47"/>
-      <c r="I13" s="52"/>
+      <c r="I13" s="54"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A14" s="46" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B14" s="46"/>
       <c r="C14" s="45" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D14" s="45"/>
       <c r="E14" s="46"/>
       <c r="F14" s="46"/>
       <c r="G14" s="49"/>
       <c r="H14" s="47"/>
-      <c r="I14" s="52"/>
+      <c r="I14" s="54"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A15" s="46" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B15" s="46"/>
       <c r="C15" s="45" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D15" s="45"/>
       <c r="E15" s="46"/>
       <c r="F15" s="46"/>
       <c r="G15" s="49" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="H15" s="47"/>
-      <c r="I15" s="52"/>
-    </row>
-    <row r="16" spans="1:9" ht="154.9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="45" t="s">
-        <v>239</v>
-      </c>
-      <c r="B16" s="45"/>
+      <c r="I15" s="54"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A16" s="46" t="s">
+        <v>315</v>
+      </c>
+      <c r="B16" s="46"/>
       <c r="C16" s="45" t="s">
-        <v>285</v>
-      </c>
-      <c r="D16" s="48"/>
+        <v>316</v>
+      </c>
+      <c r="D16" s="45"/>
       <c r="E16" s="46"/>
       <c r="F16" s="46"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="22" t="s">
-        <v>252</v>
-      </c>
-      <c r="I16" s="48"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18"/>
-      <c r="F18" s="13"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A19" s="42"/>
-      <c r="B19" s="42"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="F19" s="42"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A20" s="42"/>
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="F20" s="42"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A21" s="42"/>
-      <c r="B21" s="42"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42"/>
-      <c r="F21" s="42"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G16" s="49"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="53"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A17" s="46" t="s">
+        <v>317</v>
+      </c>
+      <c r="B17" s="46"/>
+      <c r="C17" s="45" t="s">
+        <v>318</v>
+      </c>
+      <c r="D17" s="45"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="49"/>
+      <c r="H17" s="47"/>
+      <c r="I17" s="53"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A18" s="46" t="s">
+        <v>319</v>
+      </c>
+      <c r="B18" s="46"/>
+      <c r="C18" s="45" t="s">
+        <v>320</v>
+      </c>
+      <c r="D18" s="45"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="46"/>
+      <c r="G18" s="49"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="53"/>
+    </row>
+    <row r="19" spans="1:9" ht="154.9" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="45" t="s">
+        <v>233</v>
+      </c>
+      <c r="B19" s="45"/>
+      <c r="C19" s="45" t="s">
+        <v>321</v>
+      </c>
+      <c r="D19" s="48"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="46"/>
+      <c r="H19" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="I19" s="48"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21"/>
+      <c r="F21" s="13"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A22" s="42"/>
       <c r="B22" s="42"/>
       <c r="C22" s="42"/>
       <c r="D22" s="42"/>
       <c r="F22" s="42"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="D23"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="D24"/>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A23" s="42"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="F23" s="42"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A24" s="42"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="42"/>
+      <c r="D24" s="42"/>
+      <c r="F24" s="42"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A25" s="42"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="F25" s="42"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="D26"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="D27"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2723,10 +2765,10 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" s="14" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="C1" s="15" t="s">
         <v>1</v>
@@ -2738,10 +2780,10 @@
         <v>3</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.15">
@@ -2759,10 +2801,10 @@
         <v>49</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="G2" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.15">
@@ -2780,7 +2822,7 @@
         <v>27</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.15">
@@ -2798,7 +2840,7 @@
         <v>28</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.15">
@@ -2807,7 +2849,7 @@
       </c>
       <c r="B5" s="12"/>
       <c r="C5" s="18" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>6</v>
@@ -2816,10 +2858,10 @@
         <v>29</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="G5" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.15">
@@ -2837,7 +2879,7 @@
         <v>30</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.15">
@@ -2855,7 +2897,7 @@
         <v>31</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.15">
@@ -2864,7 +2906,7 @@
       </c>
       <c r="B8" s="12"/>
       <c r="C8" s="18" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>9</v>
@@ -2873,10 +2915,10 @@
         <v>32</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="G8" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.15">
@@ -2885,7 +2927,7 @@
       </c>
       <c r="B9" s="12"/>
       <c r="C9" s="18" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="D9" s="17" t="s">
         <v>50</v>
@@ -2894,7 +2936,7 @@
         <v>51</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.15">
@@ -2912,7 +2954,7 @@
         <v>33</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.15">
@@ -2930,7 +2972,7 @@
         <v>34</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.15">
@@ -2948,7 +2990,7 @@
         <v>35</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.15">
@@ -2966,10 +3008,10 @@
         <v>36</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="G13" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.15">
@@ -2985,10 +3027,10 @@
         <v>37</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="G14" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.15">
@@ -3006,10 +3048,10 @@
         <v>38</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="G15" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="27" x14ac:dyDescent="0.15">
@@ -3027,10 +3069,10 @@
         <v>39</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="G16" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.15">
@@ -3140,13 +3182,13 @@
   <sheetData>
     <row r="1" spans="1:6" ht="27" x14ac:dyDescent="0.15">
       <c r="A1" s="24" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D1" s="24" t="s">
         <v>55</v>
@@ -3157,13 +3199,13 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2" s="22" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C2" s="38" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="D2" s="22" t="s">
         <v>62</v>
@@ -3174,14 +3216,14 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3" s="22" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B3" s="38" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C3" s="22"/>
       <c r="D3" s="38" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E3" s="38" t="s">
         <v>64</v>
@@ -3190,16 +3232,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A4" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="B4" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="C4" s="38" t="s">
+        <v>286</v>
+      </c>
+      <c r="D4" s="38" t="s">
         <v>202</v>
-      </c>
-      <c r="B4" s="38" t="s">
-        <v>203</v>
-      </c>
-      <c r="C4" s="38" t="s">
-        <v>293</v>
-      </c>
-      <c r="D4" s="38" t="s">
-        <v>207</v>
       </c>
       <c r="E4" s="38" t="s">
         <v>65</v>
@@ -3208,46 +3250,46 @@
     </row>
     <row r="5" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A5" s="12" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A6" s="12" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A7" s="12" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A8" s="12" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.15"/>
@@ -3275,42 +3317,42 @@
         <v>57</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="27" x14ac:dyDescent="0.15">
       <c r="A2" s="27" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C2" s="27"/>
       <c r="D2" s="45" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3" s="27" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C3" s="27"/>
       <c r="D3" s="27" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A4" s="27" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B4" s="27" t="s">
         <v>59</v>
@@ -3330,40 +3372,40 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A6" s="27" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C6" s="27"/>
       <c r="D6" s="27"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A7" s="27" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C7" s="27"/>
       <c r="D7" s="27"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A8" s="27" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="C8" s="27"/>
       <c r="D8" s="27"/>
     </row>
     <row r="9" spans="1:4" ht="15" x14ac:dyDescent="0.15">
       <c r="A9" s="27" t="s">
-        <v>217</v>
-      </c>
-      <c r="B9" s="53" t="s">
-        <v>315</v>
+        <v>212</v>
+      </c>
+      <c r="B9" s="52" t="s">
+        <v>308</v>
       </c>
       <c r="C9" s="41"/>
       <c r="D9" s="27"/>
@@ -3373,7 +3415,7 @@
         <v>75</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="C10" s="27" t="s">
         <v>159</v>
@@ -3382,10 +3424,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A11" s="50" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="C11" s="27"/>
       <c r="D11" s="27"/>
@@ -3395,10 +3437,10 @@
         <v>85</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="D12" s="27"/>
     </row>
